--- a/rating_clean.xlsx
+++ b/rating_clean.xlsx
@@ -1,26 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaimin Khaw\Desktop\credit-rating-deploy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkhaw\Desktop\credit-rating-deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4512DD9-3144-447E-B123-A6F9F745B664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="BoxPlot">"BoxPlot"</definedName>
+    <definedName name="Bubble">"Bubble"</definedName>
+    <definedName name="Candlestick">"Candlestick"</definedName>
+    <definedName name="Chart">"Chart"</definedName>
+    <definedName name="ChartImage">"ChartImage"</definedName>
+    <definedName name="ColumnRange">"ColumnRange"</definedName>
+    <definedName name="Dumbbell">"Dumbbell"</definedName>
+    <definedName name="Heatmap">"Heatmap"</definedName>
+    <definedName name="Histogram">"Histogram"</definedName>
+    <definedName name="Map">"Map"</definedName>
+    <definedName name="OHLC">"OHLC"</definedName>
+    <definedName name="PieChart">"PieChart"</definedName>
+    <definedName name="Scatter">"Scatter"</definedName>
+    <definedName name="Series">"Series"</definedName>
+    <definedName name="Stripe">"Stripe"</definedName>
+    <definedName name="Table">"Table"</definedName>
+    <definedName name="TreeMap">"TreeMap"</definedName>
+    <definedName name="Waterfall">"Waterfall"</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="190">
   <si>
     <t>cc</t>
   </si>
@@ -587,9 +606,6 @@
   </si>
   <si>
     <t>Zambia</t>
-  </si>
-  <si>
-    <t>B- *-</t>
   </si>
   <si>
     <t>Algeria</t>
@@ -598,7 +614,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -955,7 +971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E140"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1021,7 +1037,7 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>46</v>
@@ -1089,7 +1105,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
@@ -1106,7 +1122,7 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
@@ -1140,7 +1156,7 @@
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -1432,7 +1448,7 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1466,7 +1482,7 @@
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1738,7 +1754,7 @@
         <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1786,7 +1802,7 @@
         <v>41</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
         <v>11</v>
@@ -1806,7 +1822,7 @@
         <v>55</v>
       </c>
       <c r="E50" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -2004,7 +2020,7 @@
         <v>108</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
         <v>51</v>
@@ -2021,7 +2037,7 @@
         <v>109</v>
       </c>
       <c r="C63" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -2126,7 +2142,7 @@
         <v>66</v>
       </c>
       <c r="D69" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E69" t="s">
         <v>39</v>
@@ -2157,10 +2173,10 @@
         <v>118</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D71" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="E71" t="s">
         <v>46</v>
@@ -2279,7 +2295,7 @@
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>189</v>
+        <v>11</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -2398,7 +2414,7 @@
         <v>43</v>
       </c>
       <c r="D85" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E85" t="s">
         <v>29</v>
@@ -2588,7 +2604,7 @@
         <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -2653,7 +2669,7 @@
         <v>96</v>
       </c>
       <c r="D100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E100" t="s">
         <v>25</v>
@@ -2840,7 +2856,7 @@
         <v>41</v>
       </c>
       <c r="D111" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -2942,7 +2958,7 @@
         <v>72</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E117" t="s">
         <v>16</v>
@@ -3183,7 +3199,7 @@
         <v>84</v>
       </c>
       <c r="E131" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -3265,7 +3281,7 @@
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
         <v>7</v>
@@ -3316,10 +3332,10 @@
         <v>91</v>
       </c>
       <c r="D139" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="E139" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -3327,7 +3343,7 @@
         <v>612</v>
       </c>
       <c r="B140" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C140" t="s">
         <v>8</v>
